--- a/data/tr_data.xlsx
+++ b/data/tr_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\workplace\Trade_Robot\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F11DB86A-FA00-4109-997F-876EE065D490}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{918BEB3C-6019-44FF-B596-55D416C38A28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12190" yWindow="10010" windowWidth="20970" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="symbols" sheetId="2" r:id="rId1"/>
@@ -670,7 +670,7 @@
         <v>0.99</v>
       </c>
       <c r="K3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="L3">
         <v>1.1000000000000001</v>

--- a/data/tr_data.xlsx
+++ b/data/tr_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\workplace\Trade_Robot\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{918BEB3C-6019-44FF-B596-55D416C38A28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9305927-4FD8-4966-B406-D0D498E766C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12190" yWindow="10010" windowWidth="20970" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12190" yWindow="9340" windowWidth="20970" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="symbols" sheetId="2" r:id="rId1"/>
@@ -658,13 +658,13 @@
         <v>13800</v>
       </c>
       <c r="G3">
-        <v>0.04</v>
+        <v>0.01</v>
       </c>
       <c r="H3">
         <v>-0.01</v>
       </c>
       <c r="I3">
-        <v>1.4999999999999999E-2</v>
+        <v>0.01</v>
       </c>
       <c r="J3">
         <v>0.99</v>
@@ -805,7 +805,7 @@
         <v>15</v>
       </c>
       <c r="C5">
-        <v>14400</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
@@ -817,7 +817,7 @@
         <v>14</v>
       </c>
       <c r="C6">
-        <v>14500</v>
+        <v>18000</v>
       </c>
     </row>
   </sheetData>

--- a/data/tr_data.xlsx
+++ b/data/tr_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\workplace\Trade_Robot\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9305927-4FD8-4966-B406-D0D498E766C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1303723-F480-40BE-A7B6-EC0B7132EAEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="12190" yWindow="9340" windowWidth="20970" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="symbols" sheetId="2" r:id="rId1"/>
@@ -161,7 +161,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="24">
   <si>
     <t>symbol</t>
   </si>
@@ -190,9 +190,6 @@
     <t>h</t>
   </si>
   <si>
-    <t>TSLAUSDT</t>
-  </si>
-  <si>
     <t>bn</t>
   </si>
   <si>
@@ -230,6 +227,12 @@
   </si>
   <si>
     <t>lower_limit</t>
+  </si>
+  <si>
+    <t>BTCUSDT</t>
+  </si>
+  <si>
+    <t>decimal</t>
   </si>
 </sst>
 </file>
@@ -560,7 +563,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C16B2EB9-4E60-484E-8387-41AED7E3C590}">
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:O6"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.81640625" bestFit="1" customWidth="1"/>
@@ -575,12 +578,12 @@
     <col min="10" max="13" width="17.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
@@ -589,37 +592,40 @@
         <v>2</v>
       </c>
       <c r="E1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F1" t="s">
         <v>3</v>
       </c>
       <c r="G1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1" t="s">
         <v>16</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>17</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>18</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>19</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>20</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>21</v>
-      </c>
-      <c r="M1" t="s">
-        <v>22</v>
       </c>
       <c r="N1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A2" t="str">
         <f>"100548"</f>
         <v>100548</v>
@@ -637,13 +643,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A3" t="str">
         <f>"600499"</f>
         <v>600499</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C3" t="s">
         <v>5</v>
@@ -681,8 +687,11 @@
       <c r="N3" t="b">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A4" t="str">
         <f>"300548"</f>
         <v>300548</v>
@@ -700,7 +709,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A5" t="str">
         <f>"02698"</f>
         <v>02698</v>
@@ -718,21 +727,42 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s">
         <v>9</v>
       </c>
-      <c r="C6" t="s">
-        <v>10</v>
-      </c>
       <c r="D6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>2E-3</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>0.01</v>
+      </c>
+      <c r="H6">
+        <v>-0.01</v>
+      </c>
+      <c r="I6">
+        <v>0.01</v>
+      </c>
+      <c r="J6">
+        <v>0.99</v>
+      </c>
+      <c r="K6">
+        <v>0.02</v>
       </c>
       <c r="N6" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="O6">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -743,7 +773,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E98DAFAF-FDAC-4996-B0E5-E1FE8BFA3497}">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.453125" customWidth="1"/>
@@ -754,10 +784,10 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" t="s">
         <v>13</v>
-      </c>
-      <c r="C1" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
@@ -820,6 +850,72 @@
         <v>18000</v>
       </c>
     </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>22</v>
+      </c>
+      <c r="B7">
+        <v>80000</v>
+      </c>
+      <c r="C7">
+        <v>4.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8">
+        <v>75000</v>
+      </c>
+      <c r="C8">
+        <v>6.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9">
+        <v>70000</v>
+      </c>
+      <c r="C9">
+        <v>8.0000000000000002E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10">
+        <v>65000</v>
+      </c>
+      <c r="C10">
+        <v>1.6E-2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11">
+        <v>60000</v>
+      </c>
+      <c r="C11">
+        <v>4.8000000000000001E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12">
+        <v>50000</v>
+      </c>
+      <c r="C12">
+        <v>0.06</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/tr_data.xlsx
+++ b/data/tr_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\workplace\Trade_Robot\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1303723-F480-40BE-A7B6-EC0B7132EAEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB23B3BF-613B-4672-9CE9-F868D9711731}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="symbols" sheetId="2" r:id="rId1"/>
@@ -161,7 +161,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="26">
   <si>
     <t>symbol</t>
   </si>
@@ -233,6 +233,12 @@
   </si>
   <si>
     <t>decimal</t>
+  </si>
+  <si>
+    <t>XAUUSDT</t>
+  </si>
+  <si>
+    <t>TSLAUSDT</t>
   </si>
 </sst>
 </file>
@@ -563,7 +569,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C16B2EB9-4E60-484E-8387-41AED7E3C590}">
-  <dimension ref="A1:O6"/>
+  <dimension ref="A1:O8"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.81640625" bestFit="1" customWidth="1"/>
@@ -756,13 +762,89 @@
         <v>0.99</v>
       </c>
       <c r="K6">
-        <v>0.02</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="N6" t="b">
         <v>1</v>
       </c>
       <c r="O6">
         <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7">
+        <v>2E-3</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>0.01</v>
+      </c>
+      <c r="H7">
+        <v>-0.01</v>
+      </c>
+      <c r="I7">
+        <v>0.01</v>
+      </c>
+      <c r="J7">
+        <v>0.99</v>
+      </c>
+      <c r="K7">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="N7" t="b">
+        <v>1</v>
+      </c>
+      <c r="O7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" t="s">
+        <v>9</v>
+      </c>
+      <c r="E8">
+        <v>0.02</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0.01</v>
+      </c>
+      <c r="H8">
+        <v>-0.01</v>
+      </c>
+      <c r="I8">
+        <v>0.01</v>
+      </c>
+      <c r="J8">
+        <v>0.99</v>
+      </c>
+      <c r="K8">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="N8" t="b">
+        <v>1</v>
+      </c>
+      <c r="O8">
+        <v>2</v>
       </c>
     </row>
   </sheetData>
@@ -773,7 +855,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E98DAFAF-FDAC-4996-B0E5-E1FE8BFA3497}">
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.453125" customWidth="1"/>
@@ -916,6 +998,105 @@
         <v>0.06</v>
       </c>
     </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13">
+        <v>6000</v>
+      </c>
+      <c r="C13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14">
+        <v>4800</v>
+      </c>
+      <c r="C14">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15">
+        <v>4600</v>
+      </c>
+      <c r="C15">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>24</v>
+      </c>
+      <c r="B16">
+        <v>4400</v>
+      </c>
+      <c r="C16">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17">
+        <v>4200</v>
+      </c>
+      <c r="C17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18">
+        <v>450</v>
+      </c>
+      <c r="C18">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>25</v>
+      </c>
+      <c r="B19">
+        <v>380</v>
+      </c>
+      <c r="C19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>25</v>
+      </c>
+      <c r="B20">
+        <v>350</v>
+      </c>
+      <c r="C20">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>25</v>
+      </c>
+      <c r="B21">
+        <v>320</v>
+      </c>
+      <c r="C21">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/tr_data.xlsx
+++ b/data/tr_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\workplace\Trade_Robot\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB23B3BF-613B-4672-9CE9-F868D9711731}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31E0D9F3-7C54-4926-B871-4D2384869749}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2400" yWindow="3320" windowWidth="28800" windowHeight="15450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="symbols" sheetId="2" r:id="rId1"/>
@@ -161,7 +161,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="29">
   <si>
     <t>symbol</t>
   </si>
@@ -239,6 +239,15 @@
   </si>
   <si>
     <t>TSLAUSDT</t>
+  </si>
+  <si>
+    <t>k</t>
+  </si>
+  <si>
+    <t>f</t>
+  </si>
+  <si>
+    <t>BNBUSDT</t>
   </si>
 </sst>
 </file>
@@ -569,7 +578,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C16B2EB9-4E60-484E-8387-41AED7E3C590}">
-  <dimension ref="A1:O8"/>
+  <dimension ref="A1:O9"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.81640625" bestFit="1" customWidth="1"/>
@@ -756,7 +765,7 @@
         <v>-0.01</v>
       </c>
       <c r="I6">
-        <v>0.01</v>
+        <v>1.8E-3</v>
       </c>
       <c r="J6">
         <v>0.99</v>
@@ -794,7 +803,7 @@
         <v>-0.01</v>
       </c>
       <c r="I7">
-        <v>0.01</v>
+        <v>1.8E-3</v>
       </c>
       <c r="J7">
         <v>0.99</v>
@@ -832,7 +841,7 @@
         <v>-0.01</v>
       </c>
       <c r="I8">
-        <v>0.01</v>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="J8">
         <v>0.99</v>
@@ -844,6 +853,44 @@
         <v>1</v>
       </c>
       <c r="O8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>28</v>
+      </c>
+      <c r="C9" t="s">
+        <v>9</v>
+      </c>
+      <c r="D9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9">
+        <v>0.01</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0.01</v>
+      </c>
+      <c r="H9">
+        <v>-0.01</v>
+      </c>
+      <c r="I9">
+        <v>1.8E-3</v>
+      </c>
+      <c r="J9">
+        <v>0.99</v>
+      </c>
+      <c r="K9">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="N9" t="b">
+        <v>0</v>
+      </c>
+      <c r="O9">
         <v>2</v>
       </c>
     </row>
@@ -855,13 +902,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E98DAFAF-FDAC-4996-B0E5-E1FE8BFA3497}">
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -871,8 +918,14 @@
       <c r="C1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D1" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="str">
         <f>"600499"</f>
         <v>600499</v>
@@ -884,7 +937,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="str">
         <f>"600499"</f>
         <v>600499</v>
@@ -896,7 +949,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="str">
         <f t="shared" ref="A4:A6" si="0">"600499"</f>
         <v>600499</v>
@@ -908,7 +961,7 @@
         <v>12000</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="str">
         <f t="shared" si="0"/>
         <v>600499</v>
@@ -920,7 +973,7 @@
         <v>15000</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="str">
         <f t="shared" si="0"/>
         <v>600499</v>
@@ -932,7 +985,7 @@
         <v>18000</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>22</v>
       </c>
@@ -942,8 +995,14 @@
       <c r="C7">
         <v>4.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>1.4E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>22</v>
       </c>
@@ -953,8 +1012,14 @@
       <c r="C8">
         <v>6.0000000000000001E-3</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <v>1.4E-3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>22</v>
       </c>
@@ -964,8 +1029,14 @@
       <c r="C9">
         <v>8.0000000000000002E-3</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9">
+        <v>1.4E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>22</v>
       </c>
@@ -975,8 +1046,14 @@
       <c r="C10">
         <v>1.6E-2</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10">
+        <v>1.4E-3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>22</v>
       </c>
@@ -986,8 +1063,14 @@
       <c r="C11">
         <v>4.8000000000000001E-2</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11">
+        <v>1.4E-3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>22</v>
       </c>
@@ -997,8 +1080,14 @@
       <c r="C12">
         <v>0.06</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12">
+        <v>1.4E-3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>24</v>
       </c>
@@ -1008,8 +1097,14 @@
       <c r="C13">
         <v>2</v>
       </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D13">
+        <v>1</v>
+      </c>
+      <c r="E13">
+        <v>1.4E-3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>24</v>
       </c>
@@ -1017,10 +1112,16 @@
         <v>4800</v>
       </c>
       <c r="C14">
-        <v>2.2000000000000002</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+        <v>7</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="E14">
+        <v>1.4E-3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>24</v>
       </c>
@@ -1028,10 +1129,16 @@
         <v>4600</v>
       </c>
       <c r="C15">
-        <v>2.8</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+        <v>10</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="E15">
+        <v>1.4E-3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>24</v>
       </c>
@@ -1039,10 +1146,16 @@
         <v>4400</v>
       </c>
       <c r="C16">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+        <v>12</v>
+      </c>
+      <c r="D16">
+        <v>1</v>
+      </c>
+      <c r="E16">
+        <v>1.4E-3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>24</v>
       </c>
@@ -1050,10 +1163,16 @@
         <v>4200</v>
       </c>
       <c r="C17">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
+        <v>15</v>
+      </c>
+      <c r="D17">
+        <v>1</v>
+      </c>
+      <c r="E17">
+        <v>1.4E-3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>25</v>
       </c>
@@ -1063,8 +1182,14 @@
       <c r="C18">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="E18">
+        <v>1.4E-3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>25</v>
       </c>
@@ -1074,8 +1199,14 @@
       <c r="C19">
         <v>2</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D19">
+        <v>1</v>
+      </c>
+      <c r="E19">
+        <v>1.4E-3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>25</v>
       </c>
@@ -1085,8 +1216,14 @@
       <c r="C20">
         <v>4</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D20">
+        <v>1</v>
+      </c>
+      <c r="E20">
+        <v>1.4E-3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>25</v>
       </c>
@@ -1095,6 +1232,114 @@
       </c>
       <c r="C21">
         <v>6</v>
+      </c>
+      <c r="D21">
+        <v>1</v>
+      </c>
+      <c r="E21">
+        <v>1.4E-3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>28</v>
+      </c>
+      <c r="B22">
+        <v>1000</v>
+      </c>
+      <c r="C22">
+        <v>-1</v>
+      </c>
+      <c r="D22">
+        <v>1</v>
+      </c>
+      <c r="E22">
+        <v>1.4E-3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>28</v>
+      </c>
+      <c r="B23">
+        <v>800</v>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23">
+        <v>1</v>
+      </c>
+      <c r="E23">
+        <v>1.4E-3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>28</v>
+      </c>
+      <c r="B24">
+        <v>700</v>
+      </c>
+      <c r="C24">
+        <v>0.5</v>
+      </c>
+      <c r="D24">
+        <v>1</v>
+      </c>
+      <c r="E24">
+        <v>1.4E-3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>28</v>
+      </c>
+      <c r="B25">
+        <v>600</v>
+      </c>
+      <c r="C25">
+        <v>1</v>
+      </c>
+      <c r="D25">
+        <v>1</v>
+      </c>
+      <c r="E25">
+        <v>1.4E-3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>28</v>
+      </c>
+      <c r="B26">
+        <v>500</v>
+      </c>
+      <c r="C26">
+        <v>3</v>
+      </c>
+      <c r="D26">
+        <v>1</v>
+      </c>
+      <c r="E26">
+        <v>1.4E-3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>28</v>
+      </c>
+      <c r="B27">
+        <v>400</v>
+      </c>
+      <c r="C27">
+        <v>4</v>
+      </c>
+      <c r="D27">
+        <v>1</v>
+      </c>
+      <c r="E27">
+        <v>1.4E-3</v>
       </c>
     </row>
   </sheetData>

--- a/data/tr_data.xlsx
+++ b/data/tr_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\workplace\Trade_Robot\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31E0D9F3-7C54-4926-B871-4D2384869749}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EFFE7DE-CD0B-4FFD-97E1-7CD4524C723B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2400" yWindow="3320" windowWidth="28800" windowHeight="15450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="symbols" sheetId="2" r:id="rId1"/>
@@ -45,7 +45,55 @@
     <author>Wu Xinfeng</author>
   </authors>
   <commentList>
-    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{78565EE8-6D8B-454C-80BB-E270A4D697C6}">
+    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{44888B0D-B904-4748-9C1A-38C4F0139E16}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Wu Xinfeng:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+价格小数位数</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{98CD93E8-FC29-4051-A8A6-B5090B81A60C}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Wu Xinfeng:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+价格小数位数</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J1" authorId="0" shapeId="0" xr:uid="{78565EE8-6D8B-454C-80BB-E270A4D697C6}">
       <text>
         <r>
           <rPr>
@@ -69,7 +117,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{DE5C1F3C-AE4B-40BA-B080-FBD15B0D4C43}">
+    <comment ref="K1" authorId="0" shapeId="0" xr:uid="{DE5C1F3C-AE4B-40BA-B080-FBD15B0D4C43}">
       <text>
         <r>
           <rPr>
@@ -93,7 +141,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="0" shapeId="0" xr:uid="{93CCCF7B-CD71-40F1-93C3-CBBE8397234F}">
+    <comment ref="L1" authorId="0" shapeId="0" xr:uid="{93CCCF7B-CD71-40F1-93C3-CBBE8397234F}">
       <text>
         <r>
           <rPr>
@@ -108,7 +156,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J1" authorId="0" shapeId="0" xr:uid="{732158D5-8242-4F0B-8DFE-A14C16BAC439}">
+    <comment ref="M1" authorId="0" shapeId="0" xr:uid="{732158D5-8242-4F0B-8DFE-A14C16BAC439}">
       <text>
         <r>
           <rPr>
@@ -132,7 +180,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K1" authorId="0" shapeId="0" xr:uid="{72811802-F239-40AC-9B6D-7A5F1EA206AD}">
+    <comment ref="N1" authorId="0" shapeId="0" xr:uid="{72811802-F239-40AC-9B6D-7A5F1EA206AD}">
       <text>
         <r>
           <rPr>
@@ -161,7 +209,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="33">
   <si>
     <t>symbol</t>
   </si>
@@ -248,6 +296,18 @@
   </si>
   <si>
     <t>BNBUSDT</t>
+  </si>
+  <si>
+    <t>currency</t>
+  </si>
+  <si>
+    <t>CNY</t>
+  </si>
+  <si>
+    <t>USD</t>
+  </si>
+  <si>
+    <t>qty_decimal</t>
   </si>
 </sst>
 </file>
@@ -578,22 +638,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C16B2EB9-4E60-484E-8387-41AED7E3C590}">
-  <dimension ref="A1:O9"/>
+  <dimension ref="A1:Q9"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.81640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.81640625" customWidth="1"/>
     <col min="3" max="3" width="8.81640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.6328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.90625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.90625" customWidth="1"/>
-    <col min="7" max="7" width="16.453125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.08984375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.7265625" bestFit="1" customWidth="1"/>
-    <col min="10" max="13" width="17.08984375" customWidth="1"/>
+    <col min="5" max="5" width="8.6328125" customWidth="1"/>
+    <col min="6" max="6" width="13.90625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.90625" customWidth="1"/>
+    <col min="10" max="10" width="16.453125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.08984375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.7265625" bestFit="1" customWidth="1"/>
+    <col min="13" max="16" width="17.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -607,40 +668,46 @@
         <v>2</v>
       </c>
       <c r="E1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F1" t="s">
         <v>14</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
+        <v>23</v>
+      </c>
+      <c r="H1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" t="s">
         <v>3</v>
       </c>
-      <c r="G1" t="s">
+      <c r="J1" t="s">
         <v>15</v>
       </c>
-      <c r="H1" t="s">
+      <c r="K1" t="s">
         <v>16</v>
       </c>
-      <c r="I1" t="s">
+      <c r="L1" t="s">
         <v>17</v>
       </c>
-      <c r="J1" t="s">
+      <c r="M1" t="s">
         <v>18</v>
       </c>
-      <c r="K1" t="s">
+      <c r="N1" t="s">
         <v>19</v>
       </c>
-      <c r="L1" t="s">
+      <c r="O1" t="s">
         <v>20</v>
       </c>
-      <c r="M1" t="s">
+      <c r="P1" t="s">
         <v>21</v>
       </c>
-      <c r="N1" t="s">
+      <c r="Q1" t="s">
         <v>4</v>
       </c>
-      <c r="O1" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A2" t="str">
         <f>"100548"</f>
         <v>100548</v>
@@ -651,14 +718,17 @@
       <c r="D2" t="s">
         <v>6</v>
       </c>
-      <c r="E2">
+      <c r="E2" t="s">
+        <v>30</v>
+      </c>
+      <c r="F2">
         <v>0</v>
       </c>
-      <c r="N2" t="b">
+      <c r="Q2" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A3" t="str">
         <f>"600499"</f>
         <v>600499</v>
@@ -672,41 +742,44 @@
       <c r="D3" t="s">
         <v>6</v>
       </c>
-      <c r="E3">
+      <c r="E3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F3">
         <v>200</v>
       </c>
-      <c r="F3">
+      <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="I3">
         <v>13800</v>
       </c>
-      <c r="G3">
+      <c r="J3">
         <v>0.01</v>
       </c>
-      <c r="H3">
+      <c r="K3">
         <v>-0.01</v>
       </c>
-      <c r="I3">
+      <c r="L3">
         <v>0.01</v>
       </c>
-      <c r="J3">
+      <c r="M3">
         <v>0.99</v>
       </c>
-      <c r="K3">
+      <c r="N3">
         <v>0.02</v>
       </c>
-      <c r="L3">
+      <c r="O3">
         <v>1.1000000000000001</v>
       </c>
-      <c r="M3">
+      <c r="P3">
         <v>0.9</v>
       </c>
-      <c r="N3" t="b">
-        <v>1</v>
-      </c>
-      <c r="O3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="Q3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A4" t="str">
         <f>"300548"</f>
         <v>300548</v>
@@ -717,14 +790,17 @@
       <c r="D4" t="s">
         <v>6</v>
       </c>
-      <c r="E4">
+      <c r="E4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F4">
         <v>0</v>
       </c>
-      <c r="N4" t="b">
+      <c r="Q4" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A5" t="str">
         <f>"02698"</f>
         <v>02698</v>
@@ -735,14 +811,17 @@
       <c r="D5" t="s">
         <v>8</v>
       </c>
-      <c r="E5">
+      <c r="E5" t="s">
+        <v>30</v>
+      </c>
+      <c r="F5">
         <v>0</v>
       </c>
-      <c r="N5" t="b">
+      <c r="Q5" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>22</v>
       </c>
@@ -752,35 +831,41 @@
       <c r="D6" t="s">
         <v>9</v>
       </c>
-      <c r="E6">
+      <c r="E6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F6">
         <v>2E-3</v>
       </c>
-      <c r="F6">
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>3</v>
+      </c>
+      <c r="I6">
         <v>0</v>
       </c>
-      <c r="G6">
+      <c r="J6">
         <v>0.01</v>
       </c>
-      <c r="H6">
+      <c r="K6">
         <v>-0.01</v>
       </c>
-      <c r="I6">
-        <v>1.8E-3</v>
-      </c>
-      <c r="J6">
+      <c r="L6">
+        <v>2.5000000000000001E-3</v>
+      </c>
+      <c r="M6">
         <v>0.99</v>
       </c>
-      <c r="K6">
+      <c r="N6">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="N6" t="b">
-        <v>1</v>
-      </c>
-      <c r="O6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="Q6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -790,35 +875,41 @@
       <c r="D7" t="s">
         <v>9</v>
       </c>
-      <c r="E7">
+      <c r="E7" t="s">
+        <v>31</v>
+      </c>
+      <c r="F7">
         <v>2E-3</v>
       </c>
-      <c r="F7">
+      <c r="G7">
+        <v>2</v>
+      </c>
+      <c r="H7">
+        <v>3</v>
+      </c>
+      <c r="I7">
         <v>0</v>
       </c>
-      <c r="G7">
+      <c r="J7">
         <v>0.01</v>
       </c>
-      <c r="H7">
+      <c r="K7">
         <v>-0.01</v>
       </c>
-      <c r="I7">
+      <c r="L7">
         <v>1.8E-3</v>
       </c>
-      <c r="J7">
+      <c r="M7">
         <v>0.99</v>
       </c>
-      <c r="K7">
+      <c r="N7">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="N7" t="b">
-        <v>1</v>
-      </c>
-      <c r="O7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="Q7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>25</v>
       </c>
@@ -828,35 +919,41 @@
       <c r="D8" t="s">
         <v>9</v>
       </c>
-      <c r="E8">
+      <c r="E8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F8">
         <v>0.02</v>
       </c>
-      <c r="F8">
+      <c r="G8">
+        <v>2</v>
+      </c>
+      <c r="H8">
+        <v>2</v>
+      </c>
+      <c r="I8">
         <v>0</v>
       </c>
-      <c r="G8">
+      <c r="J8">
         <v>0.01</v>
       </c>
-      <c r="H8">
+      <c r="K8">
         <v>-0.01</v>
       </c>
-      <c r="I8">
-        <v>8.0000000000000002E-3</v>
-      </c>
-      <c r="J8">
+      <c r="L8">
+        <v>0.02</v>
+      </c>
+      <c r="M8">
         <v>0.99</v>
       </c>
-      <c r="K8">
+      <c r="N8">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="N8" t="b">
-        <v>1</v>
-      </c>
-      <c r="O8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="Q8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>28</v>
       </c>
@@ -866,37 +963,44 @@
       <c r="D9" t="s">
         <v>9</v>
       </c>
-      <c r="E9">
+      <c r="E9" t="s">
+        <v>31</v>
+      </c>
+      <c r="F9">
         <v>0.01</v>
       </c>
-      <c r="F9">
+      <c r="G9">
+        <v>2</v>
+      </c>
+      <c r="H9">
+        <v>2</v>
+      </c>
+      <c r="I9">
         <v>0</v>
       </c>
-      <c r="G9">
+      <c r="J9">
         <v>0.01</v>
       </c>
-      <c r="H9">
+      <c r="K9">
         <v>-0.01</v>
       </c>
-      <c r="I9">
+      <c r="L9">
         <v>1.8E-3</v>
       </c>
-      <c r="J9">
+      <c r="M9">
         <v>0.99</v>
       </c>
-      <c r="K9">
+      <c r="N9">
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="N9" t="b">
-        <v>0</v>
-      </c>
-      <c r="O9">
-        <v>2</v>
+      <c r="Q9" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -999,7 +1103,7 @@
         <v>1</v>
       </c>
       <c r="E7">
-        <v>1.4E-3</v>
+        <v>3.0000000000000001E-3</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.35">
@@ -1016,7 +1120,7 @@
         <v>1</v>
       </c>
       <c r="E8">
-        <v>1.4E-3</v>
+        <v>3.0000000000000001E-3</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
@@ -1033,7 +1137,7 @@
         <v>1</v>
       </c>
       <c r="E9">
-        <v>1.4E-3</v>
+        <v>3.0000000000000001E-3</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
@@ -1050,7 +1154,7 @@
         <v>1</v>
       </c>
       <c r="E10">
-        <v>1.4E-3</v>
+        <v>3.0000000000000001E-3</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
@@ -1067,7 +1171,7 @@
         <v>1</v>
       </c>
       <c r="E11">
-        <v>1.4E-3</v>
+        <v>3.0000000000000001E-3</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
@@ -1084,7 +1188,7 @@
         <v>1</v>
       </c>
       <c r="E12">
-        <v>1.4E-3</v>
+        <v>3.0000000000000001E-3</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
@@ -1095,13 +1199,13 @@
         <v>6000</v>
       </c>
       <c r="C13">
-        <v>2</v>
+        <v>-5</v>
       </c>
       <c r="D13">
         <v>1</v>
       </c>
       <c r="E13">
-        <v>1.4E-3</v>
+        <v>1.6000000000000001E-3</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
@@ -1118,7 +1222,7 @@
         <v>1</v>
       </c>
       <c r="E14">
-        <v>1.4E-3</v>
+        <v>1.6000000000000001E-3</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.35">
@@ -1135,7 +1239,7 @@
         <v>1</v>
       </c>
       <c r="E15">
-        <v>1.4E-3</v>
+        <v>1.6000000000000001E-3</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.35">
@@ -1152,7 +1256,7 @@
         <v>1</v>
       </c>
       <c r="E16">
-        <v>1.4E-3</v>
+        <v>1.6000000000000001E-3</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
@@ -1169,7 +1273,7 @@
         <v>1</v>
       </c>
       <c r="E17">
-        <v>1.4E-3</v>
+        <v>1.6000000000000001E-3</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
@@ -1186,7 +1290,7 @@
         <v>1</v>
       </c>
       <c r="E18">
-        <v>1.4E-3</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
@@ -1203,7 +1307,7 @@
         <v>1</v>
       </c>
       <c r="E19">
-        <v>1.4E-3</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
@@ -1220,7 +1324,7 @@
         <v>1</v>
       </c>
       <c r="E20">
-        <v>1.4E-3</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
@@ -1237,7 +1341,7 @@
         <v>1</v>
       </c>
       <c r="E21">
-        <v>1.4E-3</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.35">
@@ -1248,13 +1352,13 @@
         <v>1000</v>
       </c>
       <c r="C22">
-        <v>-1</v>
+        <v>-2</v>
       </c>
       <c r="D22">
         <v>1</v>
       </c>
       <c r="E22">
-        <v>1.4E-3</v>
+        <v>1.6000000000000001E-3</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
@@ -1271,7 +1375,7 @@
         <v>1</v>
       </c>
       <c r="E23">
-        <v>1.4E-3</v>
+        <v>1.6000000000000001E-3</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.35">
@@ -1282,13 +1386,13 @@
         <v>700</v>
       </c>
       <c r="C24">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="D24">
         <v>1</v>
       </c>
       <c r="E24">
-        <v>1.4E-3</v>
+        <v>1.6000000000000001E-3</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.35">
@@ -1299,13 +1403,13 @@
         <v>600</v>
       </c>
       <c r="C25">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D25">
         <v>1</v>
       </c>
       <c r="E25">
-        <v>1.4E-3</v>
+        <v>1.6000000000000001E-3</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.35">
@@ -1316,13 +1420,13 @@
         <v>500</v>
       </c>
       <c r="C26">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D26">
         <v>1</v>
       </c>
       <c r="E26">
-        <v>1.4E-3</v>
+        <v>1.6000000000000001E-3</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.35">
@@ -1333,13 +1437,13 @@
         <v>400</v>
       </c>
       <c r="C27">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D27">
         <v>1</v>
       </c>
       <c r="E27">
-        <v>1.4E-3</v>
+        <v>1.6000000000000001E-3</v>
       </c>
     </row>
   </sheetData>
